--- a/output/Vendor_Manager_Jobs_2026-03-16.xlsx
+++ b/output/Vendor_Manager_Jobs_2026-03-16.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/sourcing-procurement-manager-remote-at-lorven-technologies-inc-4385264881?position=1&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=liH6el4uwTvnkk5mCCf0zg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/sourcing-procurement-manager-remote-at-lorven-technologies-inc-4385264881?position=1&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=wcIWjMllR6Iud8unYSNiuQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/professional-services-procurement-manager-at-the-fountain-group-4386529773?position=2&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=Hlj50tFdvuu3ktlSFWNywA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/professional-services-procurement-manager-at-the-fountain-group-4386529773?position=2&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=4mIFsKnS6K1M%2FFFeTGYFMw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/manager-supply-chain-fully-remote-at-lensa-4386345690?position=3&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=MZ0vhzuD5xZJJTyjmJ%2FB4A%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/manager-supply-chain-fully-remote-at-lensa-4386345690?position=3&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=Fa53dKSwQbA1xNPtHL92WQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-manager-supply-chain-at-aurion-biotech-4386510897?position=4&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=w0beM1Eubwy1g3XV6r4GRg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-manager-supply-chain-at-aurion-biotech-4386510897?position=4&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=yJcTQ8lO%2BZjS91pZ8m%2F7ug%3D%3D</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/director-of-vendor-management-at-reserv-4385272259?position=5&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=dbbeXatO34KILrh7m2dWxg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/director-of-vendor-management-at-reserv-4385272259?position=5&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=gkls4LNw8HBdBCU29VUusQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/procurement-business-development-leader-at-procureability-4385293919?position=6&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=8vkJi%2F4SwDHhAEdnBO1j8g%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/procurement-business-development-leader-at-procureability-4385293919?position=6&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=2j40KB%2B0NB%2Flqbv7Otetcw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/procurement-manager-protein-remote-at-lensa-4386361121?position=7&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=5nJO5tHdL2KW3Q2udEFGiw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/procurement-manager-protein-remote-at-lensa-4386361121?position=7&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=%2FUqQcNf3MF3DhJT08ZN8VA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-director-of-operations-at-lensa-4386349423?position=8&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=9LME29ShWBFGnTTYSkh1wQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-director-of-operations-at-lensa-4386349423?position=8&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=ZxFbqRWe8wat6RJDZBI%2B2g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/idc-network-procurement-manager-north-america-remote-at-lingo-nova-4385259144?position=9&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=H7mpu3ugcDYI2A5grw23aw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/idc-network-procurement-manager-north-america-remote-at-lingo-nova-4385259144?position=9&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=s262fqHEpI5CvgXI4m7X%2FA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/supply-chain-program-manager-remote-at-lensa-4386339893?position=10&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=rW5s%2BaFIcWRBU0%2Fot%2BIUiQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/supply-chain-program-manager-remote-at-lensa-4386339893?position=10&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=FWSMe%2BZlWHwAB7m7mJLnEw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/operations-manager-at-bravo-cpg-4385600485?position=11&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=dHvZZrTZ86MG542UP1QGeA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/operations-manager-at-bravo-cpg-4385600485?position=11&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=R4ZrIQx5ujXG1gUGjjLXpA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/commodity-manager-service-supply-chain-management-at-otis-elevator-co-4382849382?position=12&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=33HYs1wag4%2BFHmhCD8Thgw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/commodity-manager-service-supply-chain-management-at-otis-elevator-co-4382849382?position=12&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=0j0AZaLsOcAzlXg9JlLVpw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/enterprise-contracts-manager-remote-at-lensa-4386350547?position=13&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=YUYJQdKPunRVWJgACfAKyA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/enterprise-contracts-manager-remote-at-lensa-4386350547?position=13&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=bNhCNq1W4EIZqrc%2FaV7iFg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/ofci-equipment-procurement-manager-data-centers-at-nebius-4385610411?position=14&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=ybznjk8OGjUY54AqM1du%2FQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/ofci-equipment-procurement-manager-data-centers-at-nebius-4385610411?position=14&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=elgrPz8LhL0z9RQ1B6PDbA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-engineering-manager-supply-chain-at-ladders-4384058624?position=15&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=esUXSM%2F4Z93kr0N%2BKkA2cg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-engineering-manager-supply-chain-at-ladders-4384058624?position=15&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=HKg5ZgEo%2FcvPnDKu7JzXYw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-manager-strategic-operations-at-coinbase-4386094615?position=16&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=uOffqO4lTHPhXdNqGPV%2BUw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-manager-strategic-operations-at-coinbase-4386094615?position=16&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=rkpPSuWF7BjTLW6AEBwkRA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/business-operations-manager-at-apex-systems-4386383220?position=17&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=iOzESBJG2NUW%2FYBojAbYrA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/business-operations-manager-at-apex-systems-4386383220?position=17&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=QViQMB46XnS8AJSAFcZbGQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-sales-development-manager-logistics-transportation-remote-at-thermo-fisher-scientific-4386091526?position=18&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=2edozKiM%2Fi21%2BnICG%2Ff3mg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-sales-development-manager-logistics-transportation-remote-at-thermo-fisher-scientific-4386091526?position=18&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=abClBk8GFCeBWUl%2FW2HdFQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-manager-commercial-private-label-at-iff-4386518687?position=19&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=Eo6lArgZOpN5%2FRaCaDRtxw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-manager-commercial-private-label-at-iff-4386518687?position=19&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=dKMpP889lQPNgQ1bvRDGMQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/commercial-insurance-account-manager-transportation-at-capstone-search-group-4386536960?position=20&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=Vs6RYQrzSTX%2BbBGif3qp%2Bw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/commercial-insurance-account-manager-transportation-at-capstone-search-group-4386536960?position=20&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=z%2BAaRmeX%2BgN4pXJBmwJCjQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-project-manager-vcf-at-the-redesign-group-4386362675?position=21&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=r9FHqKukPdd7Pjr4JrntOg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-project-manager-vcf-at-the-redesign-group-4386362675?position=21&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=tJswvUpoiRJ72TTpRDZHfg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/procurement-specialist-4-remote-at-lensa-4386350430?position=22&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=wDBlXCkVnvMCaQIVsl3PTQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/procurement-specialist-4-remote-at-lensa-4386350430?position=22&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=Ligq%2FUz0N5mNV0RhsE0dHA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,3135 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/procurement-data-specialist-at-sodexo-4386516058?position=23&amp;pageNum=0&amp;refId=nPt5pUkvaaryAiToKM%2BI6Q%3D%3D&amp;trackingId=pgWCWHkAzJIHPwRl3q8sOg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/procurement-data-specialist-at-sodexo-4386516058?position=23&amp;pageNum=0&amp;refId=tE7h%2BTObo53lr54tIMCi8w%3D%3D&amp;trackingId=%2BGTdqmRRjUQGV0dhaRvd3w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Cookwise.ai</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/operations-manager-at-cookwise-ai-4384299869?position=1&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=nhx7dCvL0rLbd08l1HnRXA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Data Operations Manager | $45/hr | Remote</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Crossing Hurdles</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/data-operations-manager-%2445-hr-remote-at-crossing-hurdles-4367558543?position=2&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=uni3l%2Bx1qiKCcKQficFfvg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Strategy &amp; Operations Senior Manager, Logistics</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Whatnot</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/strategy-operations-senior-manager-logistics-at-whatnot-4385283929?position=5&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=z%2BOry8spBlDx5JGoyVO7tg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Retail Operations Manager Remote</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Mercor</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/retail-operations-manager-remote-at-mercor-4386381161?position=9&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=FpoH1OBWGR8rt5AVmEQ5IQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Manager, Business Operations</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Swooped</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/manager-business-operations-at-swooped-4386384337?position=11&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=LKdMOSnICqsAHwnOMgzOyQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Business Operations Manager</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Swooped</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/business-operations-manager-at-swooped-4386382415?position=13&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=ALQ%2FQQqWxrTA3aaU09UoaQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Hospital Lab Operations Manager</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/hospital-lab-operations-manager-at-lensa-4386359159?position=14&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=hbAbm0aOi8hV%2BZWY5ia7MA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Operations Manager (Remote)</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Inspira Financial</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/operations-manager-remote-at-inspira-financial-4376808893?position=15&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=Hh%2FIAGa9ojtZ0WT2iZUA2A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>General Manager, North America</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Bitvavo-App</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/general-manager-north-america-at-bitvavo-app-4386556329?position=16&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=ZHFbhDQJtrxm%2BFDqNrwEFw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Assembly, Test, And Launch Operations Manager</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Space Ocean Corp</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/assembly-test-and-launch-operations-manager-at-space-ocean-corp-4386524960?position=17&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=EwKH0AU%2FUx1GnebWH3MQLw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Manager, Operations - Medical Record Retrieval (Remote)</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Sacramento, CA</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/manager-operations-medical-record-retrieval-remote-at-lensa-4386360074?position=18&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=UTNRnZqM%2B4cKlWvMiiw62w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Deputy Operations Manager (Remote)</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Network Runners, Inc.</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Millington, TN</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/deputy-operations-manager-remote-at-network-runners-inc-4386381718?position=19&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=oWO2GM0e%2BZ2Ms%2FrM%2FrVPlA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>General Manager / Integrator (Operations Leader – Remote)</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Talent Harbor</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/general-manager-integrator-operations-leader-%E2%80%93-remote-at-talent-harbor-4386369675?position=21&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=1iyf4LE5RiHEoViN6%2BagRw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Region Manager - North Atlantic Region - Remote</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Warrenville, IL</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/region-manager-north-atlantic-region-remote-at-lensa-4386339965?position=22&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=8v9jeRc%2Bk%2BrGNiemg9uMyA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Operations Manager (Remote)</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Network Runners, Inc.</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Millington, TN</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/operations-manager-remote-at-network-runners-inc-4386377819?position=23&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=EGjgMEnW3w5CC5P8GD%2BYvQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Business Operations Manager - US Remote</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>RemoteHunter</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/business-operations-manager-us-remote-at-remotehunter-4385608192?position=24&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=wsQ%2FGlhgrGhgVm9GFhaFsg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Head of Operations, Shared Services (US)</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Extenteam</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/head-of-operations-shared-services-us-at-extenteam-4385282411?position=25&amp;pageNum=0&amp;refId=2PE2iSHd0YSePDAOZO7oGw%3D%3D&amp;trackingId=mocgZacUo7Zh55U3aneknQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Contract Administrator I</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Luna Data Solutions, Inc.</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Texas, United States</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/contract-administrator-i-at-luna-data-solutions-inc-4385250993?position=1&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=U6YhK9jDvsqMzdopkA3iFw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Remote Administrative Assistant 1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/remote-administrative-assistant-1-at-lensa-4386356405?position=2&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=cb9eoJM1OOwMSZWGlja5Ow%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Scheduling Coordinator</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/scheduling-coordinator-at-lensa-4386358244?position=3&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=edNnD%2BWAozmHxs7Jlz0kKQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE ASSISTANT - IDRE - REMOTE</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>iMPROve Health</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/administrative-assistant-idre-remote-at-improve-health-4385276223?position=6&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=aNdmsTY39F2z4VmLhCahYA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Project Support Coordinator</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Chevron Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/project-support-coordinator-at-chevron-federal-credit-union-4386526779?position=10&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=8mbCVwny4LKS0kkupFQvrg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Remote Associate</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/remote-associate-at-lensa-4386362008?position=11&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=fK5ZE5V3DypGZHrtV%2F5TTQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Principal Contract Administrator (Remote)</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Centreville, VA</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/principal-contract-administrator-remote-at-lensa-4386347648?position=12&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=NfYuNMH1cFFCyljjBqPkvA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Virtual Assistant</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/virtual-assistant-at-lensa-4386343604?position=13&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=unD0BdKKwgznhuFb5Dy2hw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Enrollment Coordinator</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Insight Global</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/enrollment-coordinator-at-insight-global-4385258857?position=14&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=rlziptmc0C%2FWzVUBYagtLA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Project Assistant</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>HR Talent Board</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/project-assistant-at-hr-talent-board-4384080467?position=15&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=pSrwXFjlpXKM5EHoMzyeyA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Administrative Coordinator - First Aid (Remote)</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/administrative-coordinator-first-aid-remote-at-lensa-4386356318?position=16&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=SOmBGW4VTwP5PdpjMZ%2F6AQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Processor, Coordination of Benefits 7:00 am-3:30 PM PST - Remote</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/processor-coordination-of-benefits-7-00-am-3-30-pm-pst-remote-at-lensa-4386348621?position=19&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=1C0%2F%2BLsetAgFElUc11XLZA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Administrative Assistant</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Wiraa</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/administrative-assistant-at-wiraa-4385211263?position=20&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=HF4hVKdmGRzgFoQMA%2B6mCQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Administrative Assistant I</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Wiraa</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/administrative-assistant-i-at-wiraa-4385207406?position=21&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=Y%2BBEEYMHFwFlYjP4X4WKqg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Sr Contract Analyst - Remote</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Brea, CA</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/sr-contract-analyst-remote-at-lensa-4386358237?position=22&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=T93%2FvdJ%2BHeaftLZcZbcQnQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Remote: Contract Specialist III</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/remote-contract-specialist-iii-at-lensa-4386351509?position=23&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=Sp%2BoS5SYJWxScvsjo4ApgQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Military Personnel Administrative Clerk - Remote</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Wink Engineering, LLC</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/military-personnel-administrative-clerk-remote-at-wink-engineering-llc-4386524842?position=26&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=eE1BUCo4A5h66FQLySn%2BLw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Remote: Contract Specialist II</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Washington, VA</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr"/>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/remote-contract-specialist-ii-at-lensa-4386341852?position=27&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=0Hq%2B1IwA3DzqKJkzpeFyaQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Operations Dispatch Coordinator- Remote</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Raleigh, NC</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/operations-dispatch-coordinator-remote-at-lensa-4386354345?position=28&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=5ecl4ESmBqeumjgR%2FiBzsQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Contract Manager</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>LHH</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>California, United States</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/contract-manager-at-lhh-4385290425?position=29&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=JSOkXCI9o95wHV2r9Ep6Fg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Administrative Assistant IV</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Swooped</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/administrative-assistant-iv-at-swooped-4386374297?position=33&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=%2Fs4DFK5WDmiSCTo%2B7U9MAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Corporate Governance Administrator - Remote</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Anchorage, AK</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr"/>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/corporate-governance-administrator-remote-at-lensa-4386351383?position=35&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=Tuyb%2BRxUx2aMlBQBJkU4dQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Workday HCM Analyst – Contract</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>American Arbitration Association</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/workday-hcm-analyst-%E2%80%93-contract-at-american-arbitration-association-4384090625?position=36&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=ICi6f7Phm2RmCIEJym185w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Title Technician I</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>EQT Corporation</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr"/>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/title-technician-i-at-eqt-corporation-4386339854?position=37&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=rxsqha13o4zoyXPnbQUk4Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Government Contracts Manager</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/government-contracts-manager-at-lensa-4386350478?position=38&amp;pageNum=0&amp;refId=SJ00REML3oQBhcx1zfC%2Ftw%3D%3D&amp;trackingId=l1dCauTE0iOZFi%2B9Jc0pqA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Retail Construction - Materials Buyer</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Lush Fresh Handmade Cosmetics North America</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr"/>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>procurement specialist remote</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/retail-construction-materials-buyer-at-lush-fresh-handmade-cosmetics-north-america-4383399680?position=7&amp;pageNum=0&amp;refId=fdHiTQqXiFJ45BkWN6FvLw%3D%3D&amp;trackingId=ExrxqVMVT7WRGTFj0Jqsgw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>RCI-PG-15229-1 Senior Procurement Analyst</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Rangam</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Newark, NJ</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>procurement specialist remote</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/rci-pg-15229-1-senior-procurement-analyst-at-rangam-4386545763?position=8&amp;pageNum=0&amp;refId=fdHiTQqXiFJ45BkWN6FvLw%3D%3D&amp;trackingId=fMujIMBDuvw9IWFD4bh8Dw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Talent Sourcing Specialist</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Cherry Coatings</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr"/>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>procurement specialist remote</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/talent-sourcing-specialist-at-cherry-coatings-4386511602?position=9&amp;pageNum=0&amp;refId=fdHiTQqXiFJ45BkWN6FvLw%3D%3D&amp;trackingId=fg2cU8a1ldNg8m02mhv1qQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Associate, Client Operations - (Open to remote)</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>procurement specialist remote</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/associate-client-operations-open-to-remote-at-lensa-4386343692?position=21&amp;pageNum=0&amp;refId=fdHiTQqXiFJ45BkWN6FvLw%3D%3D&amp;trackingId=2OvLJXvWI5l9VbR1ibOpGQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Scheduling Specialist - REMOTE</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Community Health Systems</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr"/>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>procurement specialist remote</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/scheduling-specialist-remote-at-community-health-systems-4386516374?position=23&amp;pageNum=0&amp;refId=fdHiTQqXiFJ45BkWN6FvLw%3D%3D&amp;trackingId=AbF4mWWlk1jWW0FJvcokGw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Cloud Licensing Coordinator</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Managed Solution</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>procurement specialist remote</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/cloud-licensing-coordinator-at-managed-solution-4383150773?position=24&amp;pageNum=0&amp;refId=fdHiTQqXiFJ45BkWN6FvLw%3D%3D&amp;trackingId=OBS6jwaxfdk%2Bgsw0G3ocYQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Client Portfolio Manager – Government Contract Consulting</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Capitol 50 Consultants Inc</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr"/>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/client-portfolio-manager-%E2%80%93-government-contract-consulting-at-capitol-50-consultants-inc-4386527581?position=4&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=flNEes2aGcHsnzgsyyF2UA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Quality Control Manager</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/quality-control-manager-at-lensa-4386359236?position=5&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=EZBSdCEwtFyb7%2BCrNSqVHA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Program Manager – Contract Lifecycle Management Implementation</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Eliassen Group</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr"/>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/program-manager-%E2%80%93-contract-lifecycle-management-implementation-at-eliassen-group-4385612230?position=7&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=vEz7kHnMQ6S5K1kbCffiaQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager (Meter Data Management - CC&amp;B)</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>nTech Workforce</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/project-manager-meter-data-management-cc-b-at-ntech-workforce-4382473398?position=8&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=3Ir%2FDzqP%2Fuqiq%2BKowIsI5Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Clinical Project Manager Assistant (Homebased)</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Actalent</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh, NC</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/clinical-project-manager-assistant-homebased-at-actalent-4386513536?position=9&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=5Ze0HNBa86wqtiTcR7cUXg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Sr Project Manager</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>BMA DOORS</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Georgia, United States</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/sr-project-manager-at-bma-doors-4384065667?position=10&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=atGJasvwGKAxn1muEZUquQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Recruiting Operations Specialist</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Dexian</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr"/>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/recruiting-operations-specialist-at-dexian-4385611443?position=11&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=NXg9MyeREqiNSDmTSuucMQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Senior CMC Project Manager</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Aurion Biotech</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-cmc-project-manager-at-aurion-biotech-4386528115?position=12&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=HU1Loxox7pW3GWJsQUQjlg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Medical Office Manager (Remote)</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Talent Bridge</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr"/>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/medical-office-manager-remote-at-talent-bridge-4386300447?position=13&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=DQ9YNclHcXYXUNQuKSJofg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>100% remote - AI-First Project Manager (Hands-on LLM assistants, HIPAA, Jira, Agile, PM) - Immediate Interviews - Direct Client</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Accion Labs</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/100%25-remote-ai-first-project-manager-hands-on-llm-assistants-hipaa-jira-agile-pm-immediate-interviews-direct-client-at-accion-labs-4386337782?position=14&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=k5VbEQz4WNDbFT1jJEcgNA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Communications &amp; Change Manager</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Infojini Inc</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Montpelier, VT</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr"/>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/communications-change-manager-at-infojini-inc-4386383596?position=15&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=CMU425Ti4OVOZFjEGYoC6A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Senior Construction Project Manager (Data Center)</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>EPC Project Management Consulting, LLC</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-construction-project-manager-data-center-at-epc-project-management-consulting-llc-4386332712?position=16&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=QfIRZeA9TTH83M2LOYrPSQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Microsoft Security Compliance Manager / IT Audit  / REMOTE</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>DataEdge Consulting</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr"/>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/microsoft-security-compliance-manager-it-audit-remote-at-dataedge-consulting-4384078501?position=17&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=lVwhAz%2Bh1hE61wD81hj6qw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Head of EHS - MI US &amp; Canada</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Lensa</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/head-of-ehs-mi-us-canada-at-lensa-4386365011?position=19&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=Y4DuoJmtCpiehKe32bj%2FkA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>LN Concerts, Sr. Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Ladders</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr"/>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ln-concerts-sr-construction-project-manager-at-ladders-4384064185?position=20&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=EnUNEG7qAffQlibdJRE5hg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Senior Project Manager</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>IT Resources</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-project-manager-at-it-resources-4386371253?position=21&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=lq%2FIlCN%2BTFbcDIZaV%2FZFyA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Construction Project Manager - Quick Service Restaurant</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Stansell Construction</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Michigan, United States</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr"/>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/construction-project-manager-quick-service-restaurant-at-stansell-construction-4371935153?position=22&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=QP4Nxu84Wofexm0vLUP5DA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Senior Commercial Lines Account Manager</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Capstone Search Group</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-commercial-lines-account-manager-at-capstone-search-group-4386551294?position=23&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=93hzWMGhz79cfNvCKVvrAQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Rithum</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh, NC</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr"/>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/technical-project-manager-at-rithum-4386515260?position=24&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=du3c7qjlzoVJGMJxzy4ZoQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Lead Supplier Performance Engineer</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Westinghouse Electric Company</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Hopkins, SC</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/lead-supplier-performance-engineer-at-westinghouse-electric-company-4331598645?position=25&amp;pageNum=0&amp;refId=7u0IfYqUMCpMaADtGBPrCw%3D%3D&amp;trackingId=hEMdgUK%2B5niRG4a6vortUQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1688,6 +4816,74 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1716,7 +4912,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-16 22:54</t>
+          <t>Generated: 2026-03-16 23:01</t>
         </is>
       </c>
     </row>
@@ -1746,7 +4942,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>23</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
@@ -1807,7 +5003,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>23</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1824,73 +5020,73 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Lorven Technologies Inc.</t>
+          <t>Swooped</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>The Fountain Group</t>
+          <t>Aurion Biotech</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Aurion Biotech</t>
+          <t>Ladders</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Reserv</t>
+          <t>Capstone Search Group</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>ProcureAbility</t>
+          <t>Network Runners, Inc.</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Lingo-nova</t>
+          <t>Wiraa</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Bravo CPG</t>
+          <t>Lorven Technologies Inc.</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
@@ -1900,7 +5096,7 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Otis Elevator Co.</t>
+          <t>The Fountain Group</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
@@ -1910,7 +5106,7 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Reserv</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
@@ -1935,7 +5131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2010,7 +5206,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2040,6 +5236,46 @@
       <c r="B10" s="6" t="inlineStr">
         <is>
           <t>procurement manager remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>operations manager remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>contract administrator remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>procurement specialist remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
         </is>
       </c>
     </row>
